--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104486_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104486_W4.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.050599999999999</v>
+        <v>8.2126</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1052</v>
+        <v>5.9508</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9454</v>
+        <v>2.2618</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2871</v>
+        <v>6.2785</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0778</v>
+        <v>3.0761</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2092</v>
+        <v>3.2024</v>
       </c>
       <c r="J2" t="n">
-        <v>5.3906</v>
+        <v>5.3566</v>
       </c>
       <c r="K2" t="n">
-        <v>2.2614</v>
+        <v>2.244</v>
       </c>
       <c r="L2" t="n">
-        <v>3.1292</v>
+        <v>3.1126</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8965</v>
+        <v>0.9219000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8165</v>
+        <v>0.832</v>
       </c>
       <c r="O2" t="n">
-        <v>0.08</v>
+        <v>0.0898</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1418</v>
+        <v>0.0221</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.378</v>
+        <v>-0.4952</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2362</v>
+        <v>0.5173</v>
       </c>
       <c r="V2" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="3">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.845</v>
+        <v>5.0997</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4932</v>
+        <v>4.1789</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3518</v>
+        <v>0.9208</v>
       </c>
       <c r="G3" t="n">
-        <v>3.4227</v>
+        <v>3.4372</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4154</v>
+        <v>1.4214</v>
       </c>
       <c r="I3" t="n">
-        <v>2.0072</v>
+        <v>2.0158</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5202</v>
+        <v>3.5034</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9453</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>2.5749</v>
+        <v>2.5693</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0975</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4701</v>
+        <v>0.4873</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8514</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8953</v>
+        <v>0.6151</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0439</v>
+        <v>-0.5185</v>
       </c>
       <c r="V3" t="n">
-        <v>2.0246</v>
+        <v>2.0212</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SHURNA</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4465</v>
+        <v>4.1072</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7009</v>
+        <v>2.7426</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7456</v>
+        <v>1.3646</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8828</v>
+        <v>-1.3123</v>
       </c>
       <c r="H4" t="n">
-        <v>1.196</v>
+        <v>-0.9709</v>
       </c>
       <c r="I4" t="n">
-        <v>2.6868</v>
+        <v>-0.3415</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7972</v>
+        <v>-1.3896</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1905</v>
+        <v>-1.9175</v>
       </c>
       <c r="L4" t="n">
-        <v>2.6068</v>
+        <v>0.5279</v>
       </c>
       <c r="M4" t="n">
-        <v>1.0856</v>
+        <v>0.07729999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>1.0055</v>
+        <v>0.9467</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08</v>
+        <v>-0.8694</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0685</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2571</v>
+        <v>-0.2257</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3256</v>
+        <v>-0.3061</v>
       </c>
       <c r="V4" t="n">
-        <v>-2.1853</v>
+        <v>4.3579</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>4.3579</v>
       </c>
       <c r="X4" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>J. SHURNA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.838</v>
+        <v>2.8198</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1348</v>
+        <v>2.4458</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7032</v>
+        <v>0.374</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.3058</v>
+        <v>3.8895</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9726</v>
+        <v>1.2085</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3333</v>
+        <v>2.6811</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3497</v>
+        <v>2.7808</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.8986</v>
+        <v>0.1896</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5489000000000001</v>
+        <v>2.5912</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0439</v>
+        <v>1.1087</v>
       </c>
       <c r="N5" t="n">
-        <v>0.926</v>
+        <v>1.0189</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.8822</v>
+        <v>0.0898</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5878</v>
+        <v>0.6829</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.8147</v>
+        <v>0.4264</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8861</v>
+        <v>-0.4928</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9285</v>
+        <v>0.9192</v>
       </c>
       <c r="V5" t="n">
-        <v>4.3707</v>
+        <v>-2.1789</v>
       </c>
       <c r="W5" t="n">
-        <v>4.3707</v>
+        <v>0.1578</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7115</v>
+        <v>1.9816</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3284</v>
+        <v>0.5425</v>
       </c>
       <c r="F6" t="n">
-        <v>1.3831</v>
+        <v>1.4391</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9356</v>
+        <v>0.9386</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9436</v>
+        <v>0.9476</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.008</v>
+        <v>-0.008999999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1219</v>
+        <v>0.1037</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4258</v>
+        <v>0.4169</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.3039</v>
+        <v>-0.3132</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8138</v>
+        <v>0.8349</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2241</v>
+        <v>0.043</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8861</v>
+        <v>-0.6506999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>0.662</v>
+        <v>0.6937</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2476</v>
+        <v>1.0867</v>
       </c>
       <c r="E7" t="n">
-        <v>1.6652</v>
+        <v>1.3681</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4176</v>
+        <v>-0.2814</v>
       </c>
       <c r="G7" t="n">
-        <v>1.3664</v>
+        <v>1.3696</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6595</v>
+        <v>-0.6578000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>2.0258</v>
+        <v>2.0274</v>
       </c>
       <c r="J7" t="n">
-        <v>1.0595</v>
+        <v>1.0522</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.769</v>
+        <v>-0.7724</v>
       </c>
       <c r="L7" t="n">
-        <v>1.8285</v>
+        <v>1.8246</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3069</v>
+        <v>0.3174</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3702</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6472</v>
+        <v>0.3646</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0174</v>
+        <v>-0.8964</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>C. KRUTWIG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.3445</v>
+        <v>-0.1472</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3863</v>
+        <v>1.7989</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0418</v>
+        <v>-1.9461</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1107</v>
+        <v>1.1979</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6969</v>
+        <v>1.0426</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8077</v>
+        <v>0.1553</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.1776</v>
+        <v>1.709</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5715</v>
+        <v>0.3685</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.749</v>
+        <v>1.3405</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0669</v>
+        <v>-0.5111</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1255</v>
+        <v>0.6741</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0586</v>
+        <v>-1.1852</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1382</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2338</v>
+        <v>-0.4621</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2087</v>
+        <v>-0.2257</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0251</v>
+        <v>-0.2364</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-2.0212</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,40 +1111,40 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.619</v>
+        <v>-0.2516</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0349</v>
+        <v>-0.3927</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5841</v>
+        <v>0.1411</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4131</v>
+        <v>-0.1111</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0187</v>
+        <v>0.6979</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4318</v>
+        <v>-0.8089</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0346</v>
+        <v>-0.1836</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0346</v>
+        <v>0.5688</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.7524</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4477</v>
+        <v>0.0725</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0159</v>
+        <v>0.129</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4318</v>
+        <v>-0.0565</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.206</v>
+        <v>-0.1405</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>-0.2091</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1364</v>
+        <v>0.06859999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. KRUTWIG</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6944</v>
+        <v>-0.4658</v>
       </c>
       <c r="E10" t="n">
-        <v>1.1628</v>
+        <v>0.0832</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8571</v>
+        <v>-0.549</v>
       </c>
       <c r="G10" t="n">
-        <v>1.1899</v>
+        <v>-0.4088</v>
       </c>
       <c r="H10" t="n">
-        <v>1.0433</v>
+        <v>0.02</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1467</v>
+        <v>-0.4289</v>
       </c>
       <c r="J10" t="n">
-        <v>1.7275</v>
+        <v>0.0345</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3841</v>
+        <v>0.0345</v>
       </c>
       <c r="L10" t="n">
-        <v>1.3434</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.5375</v>
+        <v>-0.4433</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6592</v>
+        <v>-0.0144</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1967</v>
+        <v>-0.4289</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1342</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9938</v>
+        <v>-0.0569</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8861</v>
+        <v>0.0487</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1077</v>
+        <v>-0.1057</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0246</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.3461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2655</v>
+        <v>-1.4008</v>
       </c>
       <c r="E11" t="n">
-        <v>3.2299</v>
+        <v>3.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.4954</v>
+        <v>-4.6508</v>
       </c>
       <c r="G11" t="n">
-        <v>1.702</v>
+        <v>1.6898</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3422</v>
+        <v>1.3277</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3599</v>
+        <v>0.3621</v>
       </c>
       <c r="J11" t="n">
-        <v>2.8528</v>
+        <v>2.8181</v>
       </c>
       <c r="K11" t="n">
-        <v>1.1389</v>
+        <v>1.1129</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7139</v>
+        <v>1.7052</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.1507</v>
+        <v>-1.1284</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.354</v>
+        <v>-1.3432</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3551</v>
+        <v>-0.476</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2994</v>
+        <v>0.3714</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6545</v>
+        <v>-0.8474</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W11" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X11" t="n">
-        <v>-3.8243</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.9958</v>
+        <v>-2.9092</v>
       </c>
       <c r="E12" t="n">
-        <v>0.077</v>
+        <v>-0.8866000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0728</v>
+        <v>-2.0226</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.7319</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5107</v>
+        <v>-0.5165999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.2212</v>
+        <v>-0.2158</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.3352</v>
+        <v>-0.3472</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.4471</v>
+        <v>-0.4589</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3967</v>
+        <v>-0.3852</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0636</v>
+        <v>-0.0578</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3331</v>
+        <v>-0.3275</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S12" t="n">
-        <v>1.1218</v>
+        <v>0.2102</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2249</v>
+        <v>0.2832</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1031</v>
+        <v>-0.073</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.4783</v>
+        <v>-1.4764</v>
       </c>
       <c r="W12" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.0879</v>
+        <v>-6.6449</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.9431</v>
+        <v>-5.4927</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1448</v>
+        <v>-1.1522</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.0322</v>
+        <v>-2.0308</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.062</v>
+        <v>-1.0626</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.9702</v>
+        <v>-0.9681999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.9096</v>
+        <v>-2.9234</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.4861</v>
+        <v>-1.4931</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M13" t="n">
-        <v>0.8773</v>
+        <v>0.8925999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>0.4241</v>
+        <v>0.4305</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8949</v>
+        <v>-0.4564</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7652</v>
+        <v>-0.2929</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1298</v>
+        <v>-0.1634</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>11.13209999999999</v>
+        <v>11.4881</v>
       </c>
       <c r="E14" t="n">
-        <v>15.5331</v>
+        <v>15.5888</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.4009</v>
+        <v>-4.1007</v>
       </c>
       <c r="G14" t="n">
-        <v>14.1928</v>
+        <v>14.2057</v>
       </c>
       <c r="H14" t="n">
-        <v>6.529099999999999</v>
+        <v>6.533899999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>7.663399999999999</v>
+        <v>7.671799999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>12.7322</v>
+        <v>12.5145</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3513</v>
+        <v>1.227300000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>11.3813</v>
+        <v>11.2871</v>
       </c>
       <c r="M14" t="n">
-        <v>1.4608</v>
+        <v>1.6911</v>
       </c>
       <c r="N14" t="n">
-        <v>5.1781</v>
+        <v>5.3063</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.717600000000001</v>
+        <v>-3.6153</v>
       </c>
       <c r="P14" t="n">
         <v>4.440892098500626e-16</v>
       </c>
       <c r="Q14" t="n">
-        <v>-9.0733</v>
+        <v>-9.1053</v>
       </c>
       <c r="R14" t="n">
-        <v>9.073500000000001</v>
+        <v>9.105499999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.1927</v>
+        <v>-1.8572</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.2701</v>
+        <v>-0.9091000000000002</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9226000000000001</v>
+        <v>-0.9480999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.867799999999999</v>
+        <v>-0.8602000000000003</v>
       </c>
       <c r="W14" t="n">
-        <v>13.1445</v>
+        <v>13.0886</v>
       </c>
       <c r="X14" t="n">
-        <v>-14.0121</v>
+        <v>-13.9488</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5065</v>
+        <v>1.843</v>
       </c>
       <c r="E15" t="n">
-        <v>2.8575</v>
+        <v>2.142</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.351</v>
+        <v>-0.299</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9325</v>
+        <v>1.9421</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3621</v>
+        <v>1.3668</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8892</v>
+        <v>1.8824</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1429</v>
+        <v>1.1376</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0433</v>
+        <v>0.0597</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0522</v>
+        <v>0.3774</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8075</v>
+        <v>0.1019</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2447</v>
+        <v>0.2755</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3989</v>
+        <v>1.4148</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9853</v>
+        <v>1.3267</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4136</v>
+        <v>0.0881</v>
       </c>
       <c r="G16" t="n">
-        <v>0.6976</v>
+        <v>0.7085</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0434</v>
+        <v>-0.0349</v>
       </c>
       <c r="I16" t="n">
-        <v>0.741</v>
+        <v>0.7433999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2834</v>
+        <v>1.2805</v>
       </c>
       <c r="K16" t="n">
-        <v>0.052</v>
+        <v>0.0517</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2315</v>
+        <v>1.2288</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5858</v>
+        <v>-0.572</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4904</v>
+        <v>-0.4854</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>0.516</v>
+        <v>0.5274</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4174</v>
+        <v>-0.0629</v>
       </c>
       <c r="U16" t="n">
-        <v>0.9333</v>
+        <v>0.5903</v>
       </c>
       <c r="V16" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9121</v>
+        <v>1.2653</v>
       </c>
       <c r="E17" t="n">
-        <v>2.524</v>
+        <v>2.367</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.6118</v>
+        <v>-1.1016</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8514</v>
+        <v>1.839</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2915</v>
+        <v>-0.2874</v>
       </c>
       <c r="I17" t="n">
-        <v>2.1429</v>
+        <v>2.1264</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2498</v>
+        <v>3.2107</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.6203</v>
+        <v>-0.6313</v>
       </c>
       <c r="L17" t="n">
-        <v>3.8701</v>
+        <v>3.842</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3984</v>
+        <v>-1.3717</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3288</v>
+        <v>0.3438</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.7272</v>
+        <v>-1.7155</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.248</v>
+        <v>0.6037</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4083</v>
+        <v>0.2944</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1603</v>
+        <v>0.3093</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>E. VALTONEN</t>
+          <t>I. AURRECOECHEA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3378</v>
+        <v>-0.0319</v>
       </c>
       <c r="E18" t="n">
-        <v>4.6895</v>
+        <v>-0.0697</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.3518</v>
+        <v>0.0378</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.3326</v>
+        <v>-0.0144</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.3216</v>
+        <v>-0.1724</v>
       </c>
       <c r="I18" t="n">
-        <v>0.989</v>
+        <v>0.1579</v>
       </c>
       <c r="J18" t="n">
-        <v>1.222</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6113</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>2.8334</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.5547</v>
+        <v>-0.0144</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7103</v>
+        <v>-0.1724</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.8444</v>
+        <v>0.1579</v>
       </c>
       <c r="P18" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5878</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8310999999999999</v>
+        <v>-0.0174</v>
       </c>
       <c r="T18" t="n">
-        <v>0.7773</v>
+        <v>-0.0697</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0538</v>
+        <v>0.0523</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>3.8243</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-3.4387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>L. BOZIC</t>
+          <t>T. MUNNINGS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0125</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>3.7636</v>
+        <v>-0.3494</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.7511</v>
+        <v>0.2837</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.4254</v>
+        <v>0.09660000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3993</v>
+        <v>0.2725</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0262</v>
+        <v>-0.1759</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3451</v>
+        <v>-0.1194</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8463000000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1914</v>
+        <v>-0.1194</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7706</v>
+        <v>0.216</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.553</v>
+        <v>0.2725</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.2176</v>
+        <v>-0.0565</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>0.2276</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4341</v>
+        <v>-0.2323</v>
       </c>
       <c r="T19" t="n">
-        <v>1.5637</v>
+        <v>-0.2301</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8704</v>
+        <v>-0.0022</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.4498</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
-        <v>2.9889</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-3.4387</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>I. AURRECOECHEA</t>
+          <t>E. VALTONEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0646</v>
+        <v>-0.147</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.0696</v>
+        <v>3.9325</v>
       </c>
       <c r="F20" t="n">
-        <v>0.005</v>
+        <v>-4.0795</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0159</v>
+        <v>-1.3351</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1732</v>
+        <v>-2.3289</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1573</v>
+        <v>0.9938</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1.1839</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-1.6385</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.8223</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0159</v>
+        <v>-2.5189</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1732</v>
+        <v>-0.6904</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1573</v>
+        <v>-1.8285</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>0.4553</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0487</v>
+        <v>0.3458</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0696</v>
+        <v>0.0736</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0209</v>
+        <v>0.2722</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>3.8132</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2877</v>
+        <v>-0.5049</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6909</v>
+        <v>1.1933</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.9786</v>
+        <v>-1.6982</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.5253</v>
+        <v>-0.5269</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6262</v>
+        <v>0.6261</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1515</v>
+        <v>-1.153</v>
       </c>
       <c r="J21" t="n">
-        <v>1.8009</v>
+        <v>1.7779</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9107</v>
+        <v>0.8996</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8902</v>
+        <v>0.8783</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.3261</v>
+        <v>-2.3048</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2844</v>
+        <v>-0.2734</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0417</v>
+        <v>-2.0314</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1715</v>
+        <v>-0.0479</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4779</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3064</v>
+        <v>-0.0567</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. MUNNINGS</t>
+          <t>L. BOZIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3775</v>
+        <v>-1.2358</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4625</v>
+        <v>2.8675</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08500000000000001</v>
+        <v>-4.1033</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0936</v>
+        <v>-2.4402</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2669</v>
+        <v>-1.4232</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1733</v>
+        <v>-1.017</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.1147</v>
+        <v>0.2931</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>-0.8908</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1147</v>
+        <v>1.1839</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2082</v>
+        <v>-2.7334</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2669</v>
+        <v>-0.5325</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0586</v>
+        <v>-2.2009</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.2268</v>
+        <v>1.5934</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5371</v>
+        <v>1.2076</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>0.7448</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1893</v>
+        <v>0.4628</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.4584</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.9678</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-3.4262</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.2499</v>
+        <v>-3.5918</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8486</v>
+        <v>-2.153</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.4012</v>
+        <v>-1.4389</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.8871</v>
+        <v>-3.8794</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.2106</v>
+        <v>-2.2115</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6765</v>
+        <v>-1.668</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.1232</v>
+        <v>-2.1338</v>
       </c>
       <c r="K23" t="n">
-        <v>-2.2725</v>
+        <v>-2.2827</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.7639</v>
+        <v>-1.7457</v>
       </c>
       <c r="N23" t="n">
-        <v>0.0619</v>
+        <v>0.0713</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7917999999999999</v>
+        <v>-0.1465</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8861</v>
+        <v>-0.1769</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0944</v>
+        <v>0.0305</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9205</v>
+        <v>-3.6965</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7886</v>
+        <v>-2.9038</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.1319</v>
+        <v>-0.7927</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.9617</v>
+        <v>-4.9707</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.1313</v>
+        <v>-1.1316</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.8304</v>
+        <v>-3.8391</v>
       </c>
       <c r="J24" t="n">
-        <v>-4.6987</v>
+        <v>-4.7306</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.4759</v>
+        <v>-1.4898</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.2228</v>
+        <v>-3.2407</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.263</v>
+        <v>-0.2402</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.9488</v>
+        <v>-2.9592</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.995</v>
+        <v>0.2625</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7652</v>
+        <v>0.1808</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2299</v>
+        <v>0.08160000000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>3.9851</v>
+        <v>3.9709</v>
       </c>
       <c r="W24" t="n">
-        <v>5.0777</v>
+        <v>5.0604</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.3999</v>
+        <v>-5.5996</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9405</v>
+        <v>-4.2525</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.4594</v>
+        <v>-1.3471</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.6198</v>
+        <v>-5.625</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.2136</v>
+        <v>-1.2094</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.4062</v>
+        <v>-4.4156</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.3145</v>
+        <v>-4.3359</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4573</v>
+        <v>-0.4621</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.8572</v>
+        <v>-3.8737</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.3053</v>
+        <v>-1.2891</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.549</v>
+        <v>-0.5419</v>
       </c>
       <c r="P25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6875</v>
+        <v>0.1149</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6261</v>
+        <v>0.0834</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0614</v>
+        <v>0.0316</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-11.1323</v>
+        <v>-10.3501</v>
       </c>
       <c r="E26" t="n">
-        <v>4.401</v>
+        <v>4.100599999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-15.5332</v>
+        <v>-14.4507</v>
       </c>
       <c r="G26" t="n">
-        <v>-14.1927</v>
+        <v>-14.2055</v>
       </c>
       <c r="H26" t="n">
-        <v>-6.529299999999999</v>
+        <v>-6.533899999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.663399999999999</v>
+        <v>-7.671900000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>-1.460700000000001</v>
+        <v>-1.691199999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>-5.178</v>
+        <v>-5.3063</v>
       </c>
       <c r="L26" t="n">
-        <v>3.7175</v>
+        <v>3.6151</v>
       </c>
       <c r="M26" t="n">
-        <v>-12.7322</v>
+        <v>-12.5145</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.3512</v>
+        <v>-1.2274</v>
       </c>
       <c r="O26" t="n">
-        <v>-11.381</v>
+        <v>-11.287</v>
       </c>
       <c r="P26" t="n">
-        <v>9.999999999976694e-05</v>
+        <v>9.999999999948939e-05</v>
       </c>
       <c r="Q26" t="n">
-        <v>-9.073500000000001</v>
+        <v>-9.105500000000001</v>
       </c>
       <c r="R26" t="n">
-        <v>9.0733</v>
+        <v>9.105299999999998</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1928</v>
+        <v>2.9952</v>
       </c>
       <c r="T26" t="n">
-        <v>0.9225</v>
+        <v>0.9481000000000002</v>
       </c>
       <c r="U26" t="n">
-        <v>1.2702</v>
+        <v>2.0472</v>
       </c>
       <c r="V26" t="n">
-        <v>0.8677999999999999</v>
+        <v>0.8602999999999998</v>
       </c>
       <c r="W26" t="n">
-        <v>14.012</v>
+        <v>13.9489</v>
       </c>
       <c r="X26" t="n">
-        <v>-13.1444</v>
+        <v>-13.0887</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104486_W4.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104486_W4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-13.9488</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-3.4262</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104486_W4.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-13.0887</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
